--- a/从零开始学Slots/从零开始学Slots-15-基础篇-WaySlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-15-基础篇-WaySlots.xlsx
@@ -8241,6 +8241,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:I174" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8818,5 +8821,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M65" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-15-基础篇-WaySlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-15-基础篇-WaySlots.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="194">
   <si>
     <r>
       <rPr>
@@ -7149,7 +7149,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7264,6 +7264,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7625,8 +7633,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
-        <v>17</v>
+      <c r="A22" s="29">
+        <v>243</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8743,8 +8751,8 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>187</v>
+      <c r="A41" s="30">
+        <v>27</v>
       </c>
       <c r="B41" s="22" t="str">
         <f aca="false">IF(ABS(27/27-1)&lt;0.000000001,"✓","✗")</f>
